--- a/tools/config.xlsx
+++ b/tools/config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF067D17"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>正在加载目录：</t>
     </r>
     <r>
@@ -148,6 +154,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF080808"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>%{</t>
     </r>
     <r>
@@ -315,6 +327,36 @@
   </si>
   <si>
     <t>时间:</t>
+  </si>
+  <si>
+    <t>重新发牌</t>
+  </si>
+  <si>
+    <t>ui_random_deal</t>
+  </si>
+  <si>
+    <t>Random Deal</t>
+  </si>
+  <si>
+    <t>随机发牌</t>
+  </si>
+  <si>
+    <t>ui_home_page</t>
+  </si>
+  <si>
+    <t>Home Page</t>
+  </si>
+  <si>
+    <t>返回主界面</t>
+  </si>
+  <si>
+    <t>ui_replay</t>
+  </si>
+  <si>
+    <t>Replay</t>
+  </si>
+  <si>
+    <t>重玩</t>
   </si>
 </sst>
 </file>
@@ -1617,7 +1659,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="49.5192307692308" customWidth="1"/>
@@ -1801,6 +1843,50 @@
         <v>65</v>
       </c>
     </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/tools/config.xlsx
+++ b/tools/config.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27760" windowHeight="12660" activeTab="1"/>
+    <workbookView windowWidth="27760" windowHeight="12660" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="loading-language" sheetId="1" r:id="rId1"/>
     <sheet name="game1-language" sheetId="2" r:id="rId2"/>
+    <sheet name="game1-level" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="88">
   <si>
     <t>id</t>
   </si>
@@ -260,10 +261,10 @@
     <t>ui_level</t>
   </si>
   <si>
-    <t>LV:%{level}</t>
-  </si>
-  <si>
-    <t>等级:%{level}</t>
+    <t>LV:</t>
+  </si>
+  <si>
+    <t>等级:</t>
   </si>
   <si>
     <t>ui_hints</t>
@@ -357,6 +358,42 @@
   </si>
   <si>
     <t>重玩</t>
+  </si>
+  <si>
+    <t>ui_claim</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>领取</t>
+  </si>
+  <si>
+    <t>ui_current</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>当前成绩</t>
+  </si>
+  <si>
+    <t>ui_best</t>
+  </si>
+  <si>
+    <t>Best</t>
+  </si>
+  <si>
+    <t>历史最好成绩</t>
+  </si>
+  <si>
+    <t>levelId</t>
+  </si>
+  <si>
+    <t>maxExp</t>
+  </si>
+  <si>
+    <t>coin</t>
   </si>
 </sst>
 </file>
@@ -546,6 +583,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.8"/>
+      <color rgb="FF067D17"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF067D17"/>
       <name val="宋体"/>
@@ -562,13 +606,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF080808"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.8"/>
-      <color rgb="FF067D17"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1659,7 +1696,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="49.5192307692308" customWidth="1"/>
@@ -1887,6 +1924,1151 @@
         <v>75</v>
       </c>
     </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C100"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>60</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>96</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>114</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>132</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>150</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>168</v>
+      </c>
+      <c r="C11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>186</v>
+      </c>
+      <c r="C12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>204</v>
+      </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>222</v>
+      </c>
+      <c r="C14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>240</v>
+      </c>
+      <c r="C15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>258</v>
+      </c>
+      <c r="C16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>276</v>
+      </c>
+      <c r="C17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>294</v>
+      </c>
+      <c r="C18">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>312</v>
+      </c>
+      <c r="C19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>330</v>
+      </c>
+      <c r="C20">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>348</v>
+      </c>
+      <c r="C21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>366</v>
+      </c>
+      <c r="C22">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>384</v>
+      </c>
+      <c r="C23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>402</v>
+      </c>
+      <c r="C24">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>420</v>
+      </c>
+      <c r="C25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>438</v>
+      </c>
+      <c r="C26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>456</v>
+      </c>
+      <c r="C27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>474</v>
+      </c>
+      <c r="C28">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>492</v>
+      </c>
+      <c r="C29">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>510</v>
+      </c>
+      <c r="C30">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>528</v>
+      </c>
+      <c r="C31">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>546</v>
+      </c>
+      <c r="C32">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>564</v>
+      </c>
+      <c r="C33">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>582</v>
+      </c>
+      <c r="C34">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>600</v>
+      </c>
+      <c r="C35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>618</v>
+      </c>
+      <c r="C36">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>636</v>
+      </c>
+      <c r="C37">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>654</v>
+      </c>
+      <c r="C38">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>672</v>
+      </c>
+      <c r="C39">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>690</v>
+      </c>
+      <c r="C40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>708</v>
+      </c>
+      <c r="C41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>726</v>
+      </c>
+      <c r="C42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>744</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>762</v>
+      </c>
+      <c r="C44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>780</v>
+      </c>
+      <c r="C45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>798</v>
+      </c>
+      <c r="C46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>816</v>
+      </c>
+      <c r="C47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>834</v>
+      </c>
+      <c r="C48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>852</v>
+      </c>
+      <c r="C49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>870</v>
+      </c>
+      <c r="C50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>888</v>
+      </c>
+      <c r="C51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>906</v>
+      </c>
+      <c r="C52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>924</v>
+      </c>
+      <c r="C53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>942</v>
+      </c>
+      <c r="C54">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>960</v>
+      </c>
+      <c r="C55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>978</v>
+      </c>
+      <c r="C56">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>996</v>
+      </c>
+      <c r="C57">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>1014</v>
+      </c>
+      <c r="C58">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>1032</v>
+      </c>
+      <c r="C59">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>1050</v>
+      </c>
+      <c r="C60">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>1068</v>
+      </c>
+      <c r="C61">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1086</v>
+      </c>
+      <c r="C62">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>1104</v>
+      </c>
+      <c r="C63">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>1122</v>
+      </c>
+      <c r="C64">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>1140</v>
+      </c>
+      <c r="C65">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>1158</v>
+      </c>
+      <c r="C66">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>1176</v>
+      </c>
+      <c r="C67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>1194</v>
+      </c>
+      <c r="C68">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>1212</v>
+      </c>
+      <c r="C69">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>1230</v>
+      </c>
+      <c r="C70">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>1248</v>
+      </c>
+      <c r="C71">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>1266</v>
+      </c>
+      <c r="C72">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>1284</v>
+      </c>
+      <c r="C73">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>1302</v>
+      </c>
+      <c r="C74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>1320</v>
+      </c>
+      <c r="C75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>1338</v>
+      </c>
+      <c r="C76">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>1356</v>
+      </c>
+      <c r="C77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>1374</v>
+      </c>
+      <c r="C78">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>1392</v>
+      </c>
+      <c r="C79">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>1410</v>
+      </c>
+      <c r="C80">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>1428</v>
+      </c>
+      <c r="C81">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>1446</v>
+      </c>
+      <c r="C82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>1464</v>
+      </c>
+      <c r="C83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>1482</v>
+      </c>
+      <c r="C84">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>1500</v>
+      </c>
+      <c r="C85">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>1518</v>
+      </c>
+      <c r="C86">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>1536</v>
+      </c>
+      <c r="C87">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>1554</v>
+      </c>
+      <c r="C88">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>1572</v>
+      </c>
+      <c r="C89">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>1590</v>
+      </c>
+      <c r="C90">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>1608</v>
+      </c>
+      <c r="C91">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>1626</v>
+      </c>
+      <c r="C92">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>1644</v>
+      </c>
+      <c r="C93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>1662</v>
+      </c>
+      <c r="C94">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>1680</v>
+      </c>
+      <c r="C95">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>1698</v>
+      </c>
+      <c r="C96">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>1716</v>
+      </c>
+      <c r="C97">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>1734</v>
+      </c>
+      <c r="C98">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>1752</v>
+      </c>
+      <c r="C99">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>1770</v>
+      </c>
+      <c r="C100">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/tools/config.xlsx
+++ b/tools/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27760" windowHeight="12660" activeTab="2"/>
+    <workbookView windowWidth="27760" windowHeight="12660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="loading-language" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -385,6 +385,24 @@
   </si>
   <si>
     <t>历史最好成绩</t>
+  </si>
+  <si>
+    <t>ui_congratudations</t>
+  </si>
+  <si>
+    <t>Congratudations!</t>
+  </si>
+  <si>
+    <t>恭喜！</t>
+  </si>
+  <si>
+    <t>ui_ok</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>确定</t>
   </si>
   <si>
     <t>levelId</t>
@@ -583,14 +601,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8"/>
+      <sz val="10"/>
       <color rgb="FF067D17"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9.8"/>
       <color rgb="FF067D17"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1696,7 +1714,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="49.5192307692308" customWidth="1"/>
@@ -1955,6 +1973,28 @@
       </c>
       <c r="C23" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1971,13 +2011,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/tools/config.xlsx
+++ b/tools/config.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27760" windowHeight="12660" activeTab="1"/>
+    <workbookView windowWidth="25660" windowHeight="12740" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="loading-language" sheetId="1" r:id="rId1"/>
+    <sheet name="resources-language" sheetId="1" r:id="rId1"/>
     <sheet name="game1-language" sheetId="2" r:id="rId2"/>
     <sheet name="game1-level" sheetId="3" r:id="rId3"/>
+    <sheet name="game1-shop" sheetId="4" r:id="rId4"/>
+    <sheet name="game1-dailybonus" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="118">
   <si>
     <t>id</t>
   </si>
@@ -405,6 +407,48 @@
     <t>确定</t>
   </si>
   <si>
+    <t>ui_auto</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>ui_stop</t>
+  </si>
+  <si>
+    <t>Stop</t>
+  </si>
+  <si>
+    <t>停止</t>
+  </si>
+  <si>
+    <t>ui_vip</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>ui_subscribe</t>
+  </si>
+  <si>
+    <t>Subscribe</t>
+  </si>
+  <si>
+    <t>订阅</t>
+  </si>
+  <si>
+    <t>ui_free</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>免费</t>
+  </si>
+  <si>
     <t>levelId</t>
   </si>
   <si>
@@ -412,6 +456,36 @@
   </si>
   <si>
     <t>coin</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>priceType</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>countDown</t>
+  </si>
+  <si>
+    <t>subscribe</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>num</t>
   </si>
 </sst>
 </file>
@@ -608,13 +682,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8"/>
-      <color rgb="FF067D17"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF2A8C7C"/>
       <name val="宋体"/>
@@ -624,6 +691,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF080808"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8"/>
+      <color rgb="FF067D17"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1714,7 +1788,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="49.5192307692308" customWidth="1"/>
@@ -1995,6 +2069,61 @@
       </c>
       <c r="C25" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2011,13 +2140,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3106,6 +3235,242 @@
         <v>1770</v>
       </c>
       <c r="C100">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="D4">
+        <v>0.99</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5">
+        <v>1200</v>
+      </c>
+      <c r="D5">
+        <v>1.99</v>
+      </c>
+      <c r="E5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6">
+        <v>2100</v>
+      </c>
+      <c r="D6">
+        <v>2.99</v>
+      </c>
+      <c r="E6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7">
+        <v>7000</v>
+      </c>
+      <c r="D7">
+        <v>5.99</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8">
+        <v>20000</v>
+      </c>
+      <c r="D8">
+        <v>12.99</v>
+      </c>
+      <c r="E8">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8">
         <v>100</v>
       </c>
     </row>

--- a/tools/config.xlsx
+++ b/tools/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25660" windowHeight="12740" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="25200" windowHeight="12800" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="resources-language" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="131">
   <si>
     <t>id</t>
   </si>
@@ -449,6 +449,26 @@
     <t>免费</t>
   </si>
   <si>
+    <t>ui_magic_wand</t>
+  </si>
+  <si>
+    <t>Magic Wand</t>
+  </si>
+  <si>
+    <t>魔法屋</t>
+  </si>
+  <si>
+    <t>ui_magic_wand_info</t>
+  </si>
+  <si>
+    <t>Use the Magic Wand to get   
+the hidden card and 
+ transfer it to the foundation</t>
+  </si>
+  <si>
+    <t>使用魔法棒取出隐藏的卡片，并将其转移到基金会。</t>
+  </si>
+  <si>
     <t>levelId</t>
   </si>
   <si>
@@ -473,10 +493,31 @@
     <t>countDown</t>
   </si>
   <si>
+    <t>image</t>
+  </si>
+  <si>
     <t>subscribe</t>
   </si>
   <si>
+    <t>vipcoin</t>
+  </si>
+  <si>
     <t>ad</t>
+  </si>
+  <si>
+    <t>coin01</t>
+  </si>
+  <si>
+    <t>coin04</t>
+  </si>
+  <si>
+    <t>coin05</t>
+  </si>
+  <si>
+    <t>coin06</t>
+  </si>
+  <si>
+    <t>coin07</t>
   </si>
   <si>
     <t>day</t>
@@ -682,6 +723,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.8"/>
+      <color rgb="FF067D17"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF2A8C7C"/>
       <name val="宋体"/>
@@ -691,13 +739,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF080808"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.8"/>
-      <color rgb="FF067D17"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1153,9 +1194,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1714,24 +1758,24 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1742,7 +1786,7 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1753,7 +1797,7 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1764,7 +1808,7 @@
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1775,7 +1819,7 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1788,7 +1832,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="49.5192307692308" customWidth="1"/>
@@ -2124,6 +2168,28 @@
       </c>
       <c r="C30" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" ht="51" spans="1:3">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2140,13 +2206,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3247,30 +3313,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>118</v>
+      </c>
+      <c r="F1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -3278,7 +3347,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -3286,8 +3355,11 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -3295,7 +3367,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3303,8 +3375,11 @@
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -3317,8 +3392,11 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -3331,8 +3409,11 @@
       <c r="E5">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -3345,8 +3426,11 @@
       <c r="E6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -3359,8 +3443,11 @@
       <c r="E7">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -3372,6 +3459,9 @@
       </c>
       <c r="E8">
         <v>0.8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3388,13 +3478,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3402,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -3413,7 +3503,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -3424,7 +3514,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -3435,7 +3525,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3446,7 +3536,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -3457,7 +3547,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3468,7 +3558,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C8">
         <v>100</v>

--- a/tools/config.xlsx
+++ b/tools/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="12800" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="25200" windowHeight="12740" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="resources-language" sheetId="1" r:id="rId1"/>
